--- a/data/trans_orig/IQ18D_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos</t>
+          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +716,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,61; 22,62</t>
+          <t>17,44; 22,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,59; 32,41</t>
+          <t>22,32; 32,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 26,7</t>
+          <t>18,65; 26,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 21,2</t>
+          <t>11,6; 20,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,77; 25,42</t>
+          <t>18,73; 25,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 27,09</t>
+          <t>18,15; 27,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,86; 41,27</t>
+          <t>22,67; 41,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 28,41</t>
+          <t>9,59; 25,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 23,03</t>
+          <t>18,79; 22,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,92; 27,7</t>
+          <t>21,12; 28,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,66; 31,75</t>
+          <t>21,73; 32,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,89; 21,51</t>
+          <t>12,07; 21,92</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 25,76</t>
+          <t>19,3; 25,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 24,9</t>
+          <t>16,38; 24,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,35; 21,32</t>
+          <t>13,3; 20,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 17,51</t>
+          <t>8,15; 17,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,95; 27,21</t>
+          <t>19,64; 26,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 19,02</t>
+          <t>13,15; 18,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,67; 18,45</t>
+          <t>13,5; 18,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,06; 20,78</t>
+          <t>11,83; 20,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,35; 25,53</t>
+          <t>20,38; 25,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,64; 20,85</t>
+          <t>15,47; 20,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,1; 18,7</t>
+          <t>13,96; 18,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 17,71</t>
+          <t>11,21; 17,94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,05; 36,38</t>
+          <t>23,28; 38,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,18; 23,43</t>
+          <t>18,26; 23,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 15,85</t>
+          <t>12,47; 15,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 33,53</t>
+          <t>13,42; 34,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,83; 31,51</t>
+          <t>24,77; 31,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,78; 31,28</t>
+          <t>22,72; 31,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 18,2</t>
+          <t>11,07; 17,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,0</t>
+          <t>6,21; 10,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,81; 32,79</t>
+          <t>24,86; 32,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,11; 26,2</t>
+          <t>21,18; 26,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,31; 15,82</t>
+          <t>12,16; 15,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 22,09</t>
+          <t>10,65; 21,39</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,52; 30,82</t>
+          <t>22,62; 30,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 22,09</t>
+          <t>16,35; 22,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,39</t>
+          <t>16,32; 24,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 72,13</t>
+          <t>17,86; 72,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 23,66</t>
+          <t>18,83; 23,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,02; 25,5</t>
+          <t>18,77; 25,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,65; 27,71</t>
+          <t>17,56; 27,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,3; 43,83</t>
+          <t>15,01; 44,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,26; 25,69</t>
+          <t>21,54; 26,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,38; 22,96</t>
+          <t>18,36; 22,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 24,0</t>
+          <t>17,96; 24,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 46,74</t>
+          <t>18,42; 45,32</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,2</t>
+          <t>10,93; 16,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,07; 24,75</t>
+          <t>15,49; 24,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,33; 35,2</t>
+          <t>19,55; 35,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,67</t>
+          <t>6,43; 12,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,24; 24,28</t>
+          <t>11,21; 23,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,56; 29,64</t>
+          <t>17,5; 29,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,88; 18,93</t>
+          <t>14,78; 18,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,57</t>
+          <t>5,33; 10,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,8; 19,34</t>
+          <t>11,91; 18,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,93; 25,84</t>
+          <t>17,43; 25,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 25,71</t>
+          <t>18,0; 26,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,55</t>
+          <t>6,75; 10,66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1416,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,47; 32,83</t>
+          <t>24,18; 33,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,71; 30,68</t>
+          <t>20,07; 31,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,0; 20,26</t>
+          <t>14,02; 20,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,21; 22,89</t>
+          <t>8,31; 23,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,64; 24,14</t>
+          <t>18,96; 24,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,66; 30,47</t>
+          <t>19,57; 30,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,51; 15,63</t>
+          <t>12,38; 15,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,59; 35,88</t>
+          <t>7,31; 32,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,52; 27,2</t>
+          <t>22,15; 27,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,69; 28,02</t>
+          <t>20,47; 27,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,57; 16,84</t>
+          <t>13,58; 16,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 26,88</t>
+          <t>8,51; 26,14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,6; 24,13</t>
+          <t>19,36; 24,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,22; 24,09</t>
+          <t>19,3; 24,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,96; 15,97</t>
+          <t>11,63; 15,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 22,01</t>
+          <t>9,62; 23,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,63</t>
+          <t>18,5; 23,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,87; 22,46</t>
+          <t>18,93; 22,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,86; 16,96</t>
+          <t>12,82; 16,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,66; 64,6</t>
+          <t>16,02; 60,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,59; 23,07</t>
+          <t>19,51; 23,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,57; 22,44</t>
+          <t>19,42; 22,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,83; 15,73</t>
+          <t>12,77; 15,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,57; 36,38</t>
+          <t>14,65; 38,38</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,83; 17,94</t>
+          <t>14,76; 17,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,38; 17,67</t>
+          <t>14,25; 17,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,45; 18,25</t>
+          <t>14,61; 18,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,77; 31,57</t>
+          <t>9,64; 31,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,23; 20,48</t>
+          <t>16,17; 20,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,18; 19,0</t>
+          <t>14,91; 18,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,27; 17,76</t>
+          <t>14,34; 17,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,85; 19,16</t>
+          <t>9,94; 18,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,88; 18,68</t>
+          <t>16,04; 18,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,07; 17,53</t>
+          <t>15,1; 17,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,84; 17,42</t>
+          <t>14,81; 17,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,6; 20,24</t>
+          <t>10,29; 18,25</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,59; 23,11</t>
+          <t>20,53; 23,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,05; 21,31</t>
+          <t>18,99; 21,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,98; 18,19</t>
+          <t>16,1; 18,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,09; 21,95</t>
+          <t>14,05; 22,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,51</t>
+          <t>20,16; 22,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,27; 21,55</t>
+          <t>19,26; 21,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,97; 18,61</t>
+          <t>16,07; 18,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,77; 22,99</t>
+          <t>13,64; 23,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,73; 22,36</t>
+          <t>20,71; 22,3</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,47; 21,01</t>
+          <t>19,45; 21,05</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16,32; 17,97</t>
+          <t>16,26; 17,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,61</t>
+          <t>14,53; 20,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 22,51</t>
+          <t>17,49; 22,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,32; 32,27</t>
+          <t>22,51; 32,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,65; 26,89</t>
+          <t>18,66; 26,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,83</t>
+          <t>11,24; 21,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,73; 25,29</t>
+          <t>18,43; 25,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 27,46</t>
+          <t>17,88; 27,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,67; 41,09</t>
+          <t>21,68; 41,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 25,97</t>
+          <t>9,39; 26,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 22,89</t>
+          <t>18,72; 22,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,12; 28,11</t>
+          <t>21,13; 27,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,73; 32,19</t>
+          <t>21,59; 32,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 21,92</t>
+          <t>11,94; 22,16</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,3; 25,85</t>
+          <t>19,16; 25,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,38; 24,8</t>
+          <t>16,66; 25,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 20,84</t>
+          <t>13,3; 22,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 17,1</t>
+          <t>8,39; 18,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,64; 26,94</t>
+          <t>19,92; 27,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 18,53</t>
+          <t>13,15; 18,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 18,59</t>
+          <t>13,45; 18,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 20,76</t>
+          <t>11,77; 20,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,38; 25,33</t>
+          <t>20,3; 25,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 20,32</t>
+          <t>15,7; 20,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 18,47</t>
+          <t>13,92; 18,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 17,94</t>
+          <t>11,22; 18,32</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,28; 38,26</t>
+          <t>23,24; 37,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,47</t>
+          <t>18,04; 23,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 15,98</t>
+          <t>12,57; 16,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 34,28</t>
+          <t>13,73; 35,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,77; 31,4</t>
+          <t>24,8; 32,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,72; 31,41</t>
+          <t>22,69; 31,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 17,48</t>
+          <t>11,08; 17,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,14</t>
+          <t>6,24; 10,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,86; 32,44</t>
+          <t>25,05; 32,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,18; 26,22</t>
+          <t>21,15; 26,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,16; 15,5</t>
+          <t>12,17; 15,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,65; 21,39</t>
+          <t>10,71; 22,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,62; 30,45</t>
+          <t>22,67; 30,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 22,27</t>
+          <t>16,34; 22,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 24,1</t>
+          <t>15,9; 24,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 72,55</t>
+          <t>17,29; 68,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,83; 23,9</t>
+          <t>18,72; 23,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,77; 25,43</t>
+          <t>18,9; 25,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,56; 27,61</t>
+          <t>17,6; 27,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,01; 44,69</t>
+          <t>15,66; 43,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 26,16</t>
+          <t>21,39; 26,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,79</t>
+          <t>18,34; 22,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,96; 24,04</t>
+          <t>17,68; 23,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,42; 45,32</t>
+          <t>18,1; 43,65</t>
         </is>
       </c>
     </row>
@@ -1276,17 +1276,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,49</t>
+          <t>10,92; 16,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,49; 24,85</t>
+          <t>15,61; 24,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,55; 35,75</t>
+          <t>19,75; 34,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,42 +1296,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,21; 23,41</t>
+          <t>11,28; 25,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,5; 29,32</t>
+          <t>17,66; 29,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,78; 18,88</t>
+          <t>14,81; 19,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,62</t>
+          <t>5,14; 10,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,91; 18,88</t>
+          <t>11,77; 18,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,43; 25,53</t>
+          <t>17,51; 25,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,0; 26,31</t>
+          <t>18,04; 26,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,66</t>
+          <t>6,6; 10,56</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,18; 33,34</t>
+          <t>24,48; 32,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,07; 31,4</t>
+          <t>20,17; 31,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 20,13</t>
+          <t>14,09; 20,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,31; 23,1</t>
+          <t>8,28; 24,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,96; 24,41</t>
+          <t>18,86; 24,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,57; 30,09</t>
+          <t>19,68; 30,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,38; 15,59</t>
+          <t>12,42; 15,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,31; 32,97</t>
+          <t>7,31; 31,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,15; 27,14</t>
+          <t>22,3; 27,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,47; 27,55</t>
+          <t>20,62; 27,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 16,88</t>
+          <t>13,58; 17,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,51; 26,14</t>
+          <t>8,46; 24,1</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,36; 24,34</t>
+          <t>19,47; 24,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,3; 24,17</t>
+          <t>19,35; 23,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,63; 15,82</t>
+          <t>11,89; 16,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,62; 23,1</t>
+          <t>9,94; 21,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,5; 23,59</t>
+          <t>18,66; 23,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,93; 22,44</t>
+          <t>18,91; 22,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,82; 16,76</t>
+          <t>12,99; 17,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,02; 60,56</t>
+          <t>15,96; 56,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,51; 23,02</t>
+          <t>19,38; 22,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,42; 22,54</t>
+          <t>19,5; 22,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,77; 15,7</t>
+          <t>12,89; 15,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 38,38</t>
+          <t>14,99; 37,83</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,76; 17,96</t>
+          <t>14,79; 18,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,25; 17,61</t>
+          <t>14,39; 17,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,2</t>
+          <t>14,52; 18,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,64; 31,82</t>
+          <t>9,9; 30,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,17; 20,44</t>
+          <t>16,25; 20,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,91; 18,85</t>
+          <t>15,04; 19,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,34; 17,78</t>
+          <t>14,34; 17,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,94; 18,64</t>
+          <t>9,92; 18,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,04; 18,83</t>
+          <t>16,07; 19,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,1; 17,72</t>
+          <t>15,15; 17,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,81; 17,44</t>
+          <t>14,84; 17,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,29; 18,25</t>
+          <t>10,33; 18,52</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,53; 23,06</t>
+          <t>20,58; 23,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,99; 21,2</t>
+          <t>19,01; 21,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,1; 18,37</t>
+          <t>16,06; 18,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,05; 22,45</t>
+          <t>14,3; 22,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,16; 22,36</t>
+          <t>20,18; 22,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,26; 21,75</t>
+          <t>19,24; 21,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,07; 18,57</t>
+          <t>16,01; 18,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,64; 23,75</t>
+          <t>13,63; 22,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,71; 22,3</t>
+          <t>20,67; 22,35</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,45; 21,05</t>
+          <t>19,47; 21,02</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16,26; 17,96</t>
+          <t>16,31; 17,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,53; 20,56</t>
+          <t>14,55; 20,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Provincia-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
+          <t>Tiempo medio en minutos que tuvieron que esperar desde que llegaron hasta ser atendidos/as en la última consulta médica (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21,7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28,18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14,07</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,87</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>26,96</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>22,21</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,18</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>16,38</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,58</t>
+          <t>15,2</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,49; 22,34</t>
+          <t>18,77; 25,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,51; 32,2</t>
+          <t>18,01; 27,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,66; 26,32</t>
+          <t>21,86; 41,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 21,08</t>
+          <t>9,21; 25,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,43; 25,31</t>
+          <t>17,61; 22,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,88; 27,29</t>
+          <t>22,59; 32,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,68; 41,17</t>
+          <t>18,98; 26,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 26,95</t>
+          <t>12,01; 21,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,72; 22,96</t>
+          <t>18,88; 23,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,13; 27,9</t>
+          <t>20,92; 27,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,59; 32,63</t>
+          <t>21,66; 31,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,94; 22,16</t>
+          <t>11,62; 20,34</t>
         </is>
       </c>
     </row>
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15,6</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,77</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15,75</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>22,07</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,91</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,76</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,35</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,75</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,6</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11,73</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>22,43</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17,78</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15,77</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15,96</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22,43</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17,78</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>15,77</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>13,83</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,16; 25,85</t>
+          <t>19,95; 27,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 25,4</t>
+          <t>13,12; 19,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 22,04</t>
+          <t>13,67; 18,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 18,03</t>
+          <t>11,8; 20,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,92; 27,34</t>
+          <t>19,02; 25,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 18,85</t>
+          <t>16,61; 24,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,48</t>
+          <t>13,35; 21,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,77; 20,67</t>
+          <t>8,21; 16,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,3; 25,24</t>
+          <t>20,35; 25,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,7; 20,7</t>
+          <t>15,64; 20,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 18,61</t>
+          <t>14,1; 18,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 18,32</t>
+          <t>10,75; 17,13</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27,71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26,19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,04</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>27,73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>20,51</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13,97</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>27,71</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26,19</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,04</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,23</t>
+          <t>19,28</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,16</t>
+          <t>13,85</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,24; 37,93</t>
+          <t>24,83; 31,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 23,49</t>
+          <t>22,78; 31,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 16,02</t>
+          <t>11,19; 18,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,73; 35,55</t>
+          <t>6,11; 9,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,8; 32,06</t>
+          <t>23,05; 36,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,69; 31,05</t>
+          <t>18,18; 23,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 17,04</t>
+          <t>12,45; 15,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,0</t>
+          <t>12,85; 31,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,05; 32,69</t>
+          <t>24,81; 32,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,15; 26,21</t>
+          <t>21,11; 26,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,17; 15,78</t>
+          <t>12,31; 15,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 22,83</t>
+          <t>10,32; 21,52</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21,07</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,85</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21,66</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24,82</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>25,54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>18,75</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19,02</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30,77</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,07</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,85</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,66</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,32</t>
+          <t>27,51</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,38</t>
+          <t>26,13</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,67; 30,56</t>
+          <t>18,79; 23,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 22,24</t>
+          <t>19,02; 25,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,9; 24,16</t>
+          <t>17,65; 27,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 68,28</t>
+          <t>15,51; 44,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 23,81</t>
+          <t>22,52; 30,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,9; 25,79</t>
+          <t>16,31; 22,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,6; 27,28</t>
+          <t>16,24; 24,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,66; 43,96</t>
+          <t>15,62; 65,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,39; 26,09</t>
+          <t>21,26; 25,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,34; 22,71</t>
+          <t>18,38; 22,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 23,97</t>
+          <t>17,68; 24,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,1; 43,65</t>
+          <t>17,76; 43,33</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15,1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,31</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,63</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8,38</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>13,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19,46</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>24,85</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,91</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,1</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,31</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,63</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,4</t>
+          <t>8,9</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,62</t>
+          <t>8,61</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,92; 16,5</t>
+          <t>11,24; 24,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 24,51</t>
+          <t>17,56; 29,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,75; 34,29</t>
+          <t>14,88; 18,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,43; 12,15</t>
+          <t>5,38; 10,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,28; 25,2</t>
+          <t>10,84; 16,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 29,26</t>
+          <t>15,07; 24,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,81; 19,03</t>
+          <t>19,33; 35,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,64</t>
+          <t>6,48; 12,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 18,64</t>
+          <t>11,8; 19,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 25,09</t>
+          <t>17,93; 25,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,04; 26,1</t>
+          <t>17,7; 25,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 10,56</t>
+          <t>6,8; 10,55</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21,34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23,32</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13,99</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12,93</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>27,79</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>24,18</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>16,09</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,2</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,34</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,32</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,99</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>12,57</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,89</t>
+          <t>12,79</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,48; 32,78</t>
+          <t>18,64; 24,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,17; 31,2</t>
+          <t>19,66; 30,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 20,37</t>
+          <t>12,51; 15,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,28; 24,12</t>
+          <t>7,56; 34,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,86; 24,29</t>
+          <t>24,47; 32,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 30,51</t>
+          <t>19,71; 30,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,42; 15,76</t>
+          <t>14,0; 20,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,31; 31,6</t>
+          <t>8,34; 24,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,3; 27,22</t>
+          <t>22,52; 27,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,62; 27,81</t>
+          <t>20,69; 28,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,11</t>
+          <t>13,57; 16,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 24,1</t>
+          <t>8,56; 25,21</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20,73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20,44</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14,61</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27,99</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>21,54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>21,27</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>13,58</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14,71</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20,73</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,44</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,61</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,81</t>
+          <t>15,73</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,67</t>
+          <t>22,6</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,47; 24,03</t>
+          <t>18,39; 23,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,35; 23,84</t>
+          <t>18,87; 22,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,89; 16,02</t>
+          <t>12,86; 16,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,94; 21,73</t>
+          <t>16,85; 64,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,66; 23,88</t>
+          <t>19,6; 24,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,91; 22,55</t>
+          <t>19,22; 24,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,99; 17,44</t>
+          <t>11,96; 15,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,96; 56,88</t>
+          <t>11,15; 22,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,38; 22,99</t>
+          <t>19,59; 23,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,5; 22,57</t>
+          <t>19,57; 22,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,89; 15,71</t>
+          <t>12,83; 15,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,99; 37,83</t>
+          <t>15,12; 37,2</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18,18</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>16,77</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15,75</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11,68</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>16,26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>15,84</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>16,08</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14,26</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>18,18</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>16,77</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,75</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,1</t>
+          <t>14,01</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>12,55</t>
         </is>
       </c>
     </row>
@@ -1696,52 +1696,52 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,79; 18,21</t>
+          <t>16,23; 20,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,39; 17,67</t>
+          <t>15,18; 19,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,52; 18,36</t>
+          <t>14,27; 17,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,9; 30,93</t>
+          <t>9,68; 17,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,25; 20,49</t>
+          <t>14,83; 17,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,04; 19,23</t>
+          <t>14,38; 17,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,34; 17,81</t>
+          <t>14,45; 18,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,92; 18,36</t>
+          <t>9,83; 30,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,07; 19,0</t>
+          <t>15,88; 18,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,15; 17,65</t>
+          <t>15,07; 17,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,52</t>
+          <t>10,48; 18,97</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>21,2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20,34</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>17,11</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17,07</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>21,68</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>20,1</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>17,02</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>16,99</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>21,2</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>20,34</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,97</t>
+          <t>16,59</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>16,86</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,58; 23,14</t>
+          <t>20,12; 22,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,01; 21,25</t>
+          <t>19,27; 21,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,06; 18,27</t>
+          <t>15,97; 18,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,3; 22,63</t>
+          <t>13,8; 23,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,18; 22,44</t>
+          <t>20,59; 23,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,24; 21,49</t>
+          <t>19,05; 21,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,51</t>
+          <t>15,98; 18,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,63; 22,59</t>
+          <t>13,84; 20,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,67; 22,35</t>
+          <t>20,73; 22,36</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,47; 21,02</t>
+          <t>19,47; 21,01</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16,31; 17,96</t>
+          <t>16,32; 17,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,73</t>
+          <t>14,58; 20,29</t>
         </is>
       </c>
     </row>
